--- a/06_코드/qa/manual_check/J5_코드값_봉인.xlsx
+++ b/06_코드/qa/manual_check/J5_코드값_봉인.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="봉인_코드값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="코드값(봉인)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,10 +28,17 @@
     <font>
       <b val="1"/>
       <color rgb="001E2761"/>
-      <sz val="12"/>
+      <sz val="16"/>
     </font>
     <font>
-      <color rgb="0052514E"/>
+      <color rgb="005A5A55"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="006B6B66"/>
       <sz val="9"/>
     </font>
     <font>
@@ -39,8 +46,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +60,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001E2761"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F0FA"/>
+        <fgColor rgb="00EFEFE9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F7F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,31 +94,49 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C3C2B7"/>
+        <color rgb="00C8C7BC"/>
       </left>
       <right style="thin">
-        <color rgb="00C3C2B7"/>
+        <color rgb="00C8C7BC"/>
       </right>
       <top style="thin">
-        <color rgb="00C3C2B7"/>
+        <color rgb="00C8C7BC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C3C2B7"/>
+        <color rgb="00C8C7BC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,441 +502,502 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>J-5 대조용 코드 산출값 (봉인)</t>
+          <t>코드 산출값 — 봉인</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>★ 수기 워크시트를 모두 채우고 저장한 뒤에 열 것. 먼저 보면 블라인드 검산이 성립하지 않는다.</t>
+          <t>수기 워크시트를 전부 채우고 저장한 뒤에만 여십시오</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>L2 · 010120 ADTV90·시즈닝</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>■ 먼저 읽으십시오</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>코드 산출값</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  이 파일을 미리 열면 수기 검산이 성립하지 않습니다. 답을 본 뒤의 계산은 검증이 아닙니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>관측창 개장일수 (목표 90)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>그중 정지일수</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  워크시트를 다 채웠다면, 아래 값을 09 대조표 F열에 옮겨 적으십시오.</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>그중 무거래일수</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>0</v>
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>검산 항목</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>코드값</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>산출 근거</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>그중 자료결측일수</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>0</v>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>자료마감일</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>룰북 §5.2 · 공통 개장일 축 5거래일 역산</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>ADTV90 분모 (90 − 결측일수)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>03-04</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>KTOS ADTV90</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>315,154,781.22</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>official_adtv90 · 방법 ZERO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ADTV90 분자 (거래대금 합)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>03-04</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>ADTV90 분모(개장일수)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>정지 0일은 0으로 넣고 분모에 포함 · 결측 0일</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>공식 ADTV90 (정지일 0 반영)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>114229271088.8889</v>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>미국 P10 하한</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>316,884,754.04</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>n=8 · h=(n−1)×0.10=0.7 · 선형보간</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>진단값 (정지일 분모 제외)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>114229271088.8889</v>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>KTOS 편입 여부</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>편입/제외</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>ADTV90 315,154,781.22 &lt; P10 316,884,754.04</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>시즈닝 유효관측일수</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>118</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>P10 미만 종목 수</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>h&lt;1 이므로 항상 최솟값 1개만 미달</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>시즈닝 판정 (≥90)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>SEASONED</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>2종목 이상 탈락에 필요한 최소 n</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>h=(n−1)×0.10 ≥ 1 이 되는 최소 n</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>KR 시장 P10 하한</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>목표비중 합계 (3/31 회차)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>1.000000</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>6셀 × 1/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>최대 비중 종목의 비중 (3/31 회차)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>16.6667</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>KTOS · 셀에 1종목뿐이라 1/6을 단독 보유</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>L3 · 시장별 P10 하한 · 편입 결과</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-07 지수 레벨</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>1,023.8016</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>기준일 2026-04-01=1,000 · SEGMENT_RELINK · SAME_DAY_ECOS</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>코드 산출값</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>04-13 조정 전 수익률</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>-77.26</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>179,200 ÷ 788,000 − 1 · 실재하지 않는 하락</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>P10 하한 (KR)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>73914096486.05334</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>P10 하한 (US)</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>308975201.0855556</v>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>04-13 조정 후 수익률</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>179,200 ÷ 157,600 − 1 · 분할 기준가 대비 실제 시장 반응</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>편입 종목수</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>15</v>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>■ 불일치가 났을 때</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>비중 총합</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>0.999999999999999</v>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  코드가 맞고 수기가 틀렸을 수도, 그 반대일 수도 있습니다. 어느 쪽인지 따지는 것이 이 절차의 목적입니다.</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 064400</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>0.0833333333333333</v>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자주 갈리는 지점: ADTV90 분모(90인가 87인가) · 환율을 한국 종목에도 곱했는가 · 분할 조정 경계일</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 307950</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 TER</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 ANET</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 ALAB</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 010120</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 267260</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 298040</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 GEV</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 ETN</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 APH</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 012450</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 064350</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 079550</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비중 KTOS</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>0.1666666666666666</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>L4 · 일별 지수레벨</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>코드 지수레벨</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>1023.801566757947</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>1076.495915509196</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>1057.307314585083</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>1087.217428758063</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>1065.255617307987</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>1080.971143677037</v>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  불일치를 발견하면 지우지 말고 09 대조표 H열에 원인을 적은 뒤 팀에 공유하십시오.</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/06_코드/qa/manual_check/J5_코드값_봉인.xlsx
+++ b/06_코드/qa/manual_check/J5_코드값_봉인.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -110,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,10 +130,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -629,10 +635,8 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>315,154,781.22</t>
-        </is>
+      <c r="E10" s="10" t="n">
+        <v>315154781.2222222</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
@@ -661,10 +665,8 @@
           <t>일</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="E11" s="11" t="n">
+        <v>90</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
@@ -693,10 +695,8 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>316,884,754.04</t>
-        </is>
+      <c r="E12" s="10" t="n">
+        <v>316884754.0355556</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
@@ -757,10 +757,8 @@
           <t>개</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E14" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
@@ -789,10 +787,8 @@
           <t>개</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="E15" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
@@ -821,10 +817,8 @@
           <t>비율</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
+      <c r="E16" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
@@ -853,14 +847,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>16.6667</t>
-        </is>
+      <c r="E17" s="12" t="n">
+        <v>16.66666666666666</v>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>KTOS · 셀에 1종목뿐이라 1/6을 단독 보유</t>
+          <t>KTOS · 셀에 1종목뿐이라 1/6을 단독 보유 · 단위 %</t>
         </is>
       </c>
     </row>
@@ -885,10 +877,8 @@
           <t>포인트</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>1,023.8016</t>
-        </is>
+      <c r="E18" s="10" t="n">
+        <v>1023.801566757947</v>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
@@ -917,14 +907,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>-77.26</t>
-        </is>
+      <c r="E19" s="12" t="n">
+        <v>-77.25888324873095</v>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>179,200 ÷ 788,000 − 1 · 실재하지 않는 하락</t>
+          <t>179,200 ÷ 788,000 − 1 · 실재하지 않는 하락 · 단위 %</t>
         </is>
       </c>
     </row>
@@ -949,40 +937,38 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>13.71</t>
-        </is>
+      <c r="E20" s="12" t="n">
+        <v>13.70558375634518</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>179,200 ÷ 157,600 − 1 · 분할 기준가 대비 실제 시장 반응</t>
+          <t>179,200 ÷ 157,600 − 1 · 분할 기준가 대비 실제 시장 반응 · 단위 %</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>■ 불일치가 났을 때</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  코드가 맞고 수기가 틀렸을 수도, 그 반대일 수도 있습니다. 어느 쪽인지 따지는 것이 이 절차의 목적입니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  자주 갈리는 지점: ADTV90 분모(90인가 87인가) · 환율을 한국 종목에도 곱했는가 · 분할 조정 경계일</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  불일치를 발견하면 지우지 말고 09 대조표 H열에 원인을 적은 뒤 팀에 공유하십시오.</t>
         </is>
